--- a/ANm/aggregate_Lanyuak_results.xlsx
+++ b/ANm/aggregate_Lanyuak_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +417,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Maize</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Wheat</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Barley</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Potato</t>
         </is>
@@ -458,562 +446,562 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49.95585706766354</v>
+        <v>32.45450093957344</v>
       </c>
       <c r="B3" t="n">
-        <v>50.04259018289687</v>
+        <v>32.54120369254701</v>
       </c>
       <c r="C3" t="n">
-        <v>50.04259018289687</v>
+        <v>32.54120369254701</v>
       </c>
       <c r="D3" t="n">
-        <v>47.94943694561928</v>
+        <v>30.44878310155576</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>28.32197305839554</v>
+        <v>18.37534225607473</v>
       </c>
       <c r="B4" t="n">
-        <v>28.37133254267779</v>
+        <v>18.42455325817038</v>
       </c>
       <c r="C4" t="n">
-        <v>28.37133254267779</v>
+        <v>18.42455325817038</v>
       </c>
       <c r="D4" t="n">
-        <v>27.18030922766733</v>
+        <v>17.2371117690102</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19.36145135221384</v>
+        <v>12.52424168721829</v>
       </c>
       <c r="B5" t="n">
-        <v>19.3954826555889</v>
+        <v>12.55796831781758</v>
       </c>
       <c r="C5" t="n">
-        <v>19.3954826555889</v>
+        <v>12.55796831781758</v>
       </c>
       <c r="D5" t="n">
-        <v>18.57460397299733</v>
+        <v>11.74443635287465</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>14.5195502525926</v>
+        <v>9.347678792211772</v>
       </c>
       <c r="B6" t="n">
-        <v>14.54541439663592</v>
+        <v>9.373071173212495</v>
       </c>
       <c r="C6" t="n">
-        <v>14.54541439663592</v>
+        <v>9.373071173212495</v>
       </c>
       <c r="D6" t="n">
-        <v>13.92187486410222</v>
+        <v>8.760902543980649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11.81309131829684</v>
+        <v>7.559525069141027</v>
       </c>
       <c r="B7" t="n">
-        <v>11.83448878639607</v>
+        <v>7.580286138911873</v>
       </c>
       <c r="C7" t="n">
-        <v>11.83448878639607</v>
+        <v>7.580286138911873</v>
       </c>
       <c r="D7" t="n">
-        <v>11.31898021919778</v>
+        <v>7.080109656229827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>10.22758928560422</v>
+        <v>6.501616058236422</v>
       </c>
       <c r="B8" t="n">
-        <v>10.24645215991104</v>
+        <v>6.51968601142795</v>
       </c>
       <c r="C8" t="n">
-        <v>10.24645215991104</v>
+        <v>6.51968601142795</v>
       </c>
       <c r="D8" t="n">
-        <v>9.792336578109134</v>
+        <v>6.084664434346948</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9.236695795463689</v>
+        <v>5.832259267710119</v>
       </c>
       <c r="B9" t="n">
-        <v>9.254040221189499</v>
+        <v>5.84866427369666</v>
       </c>
       <c r="C9" t="n">
-        <v>9.254040221189499</v>
+        <v>5.84866427369666</v>
       </c>
       <c r="D9" t="n">
-        <v>8.836781837796446</v>
+        <v>5.45401676945905</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8.56500868809826</v>
+        <v>5.372516620707103</v>
       </c>
       <c r="B10" t="n">
-        <v>8.581372679127904</v>
+        <v>5.387804993878016</v>
       </c>
       <c r="C10" t="n">
-        <v>8.581372679127904</v>
+        <v>5.387804993878016</v>
       </c>
       <c r="D10" t="n">
-        <v>8.18797427425163</v>
+        <v>5.020282969862691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8.067651472463083</v>
+        <v>5.028147961998831</v>
       </c>
       <c r="B11" t="n">
-        <v>8.083322303212432</v>
+        <v>5.042616922230152</v>
       </c>
       <c r="C11" t="n">
-        <v>8.083322303212432</v>
+        <v>5.042616922230152</v>
       </c>
       <c r="D11" t="n">
-        <v>7.706838291663023</v>
+        <v>4.695032302785894</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7.668096102969675</v>
+        <v>4.749291621783328</v>
       </c>
       <c r="B12" t="n">
-        <v>7.683229176497822</v>
+        <v>4.763105969170316</v>
       </c>
       <c r="C12" t="n">
-        <v>7.683229176497822</v>
+        <v>4.763105969170316</v>
       </c>
       <c r="D12" t="n">
-        <v>7.319897154276504</v>
+        <v>4.431467381160583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7.325744365614075</v>
+        <v>4.509431356936228</v>
       </c>
       <c r="B13" t="n">
-        <v>7.340425579986136</v>
+        <v>4.52268581773922</v>
       </c>
       <c r="C13" t="n">
-        <v>7.340425579986136</v>
+        <v>4.52268581773922</v>
       </c>
       <c r="D13" t="n">
-        <v>6.988161228308935</v>
+        <v>4.204693964394409</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7.018931343952005</v>
+        <v>4.294362689345789</v>
       </c>
       <c r="B14" t="n">
-        <v>7.033209883784134</v>
+        <v>4.307114744795835</v>
       </c>
       <c r="C14" t="n">
-        <v>7.033209883784134</v>
+        <v>4.307114744795835</v>
       </c>
       <c r="D14" t="n">
-        <v>6.690815542517275</v>
+        <v>4.001370061529347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6.735986444209312</v>
+        <v>4.096386430596401</v>
       </c>
       <c r="B15" t="n">
-        <v>6.74989204482582</v>
+        <v>4.108673630090057</v>
       </c>
       <c r="C15" t="n">
-        <v>6.74989204482582</v>
+        <v>4.108673630090057</v>
       </c>
       <c r="D15" t="n">
-        <v>6.416640002369955</v>
+        <v>3.814258375512475</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6.470523611651605</v>
+        <v>3.911247413999315</v>
       </c>
       <c r="B16" t="n">
-        <v>6.484075656879152</v>
+        <v>3.923096517930489</v>
       </c>
       <c r="C16" t="n">
-        <v>6.484075656879152</v>
+        <v>3.923096517930489</v>
       </c>
       <c r="D16" t="n">
-        <v>6.159488529745016</v>
+        <v>3.6393540528446</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6.218957075385667</v>
+        <v>3.736518707733344</v>
       </c>
       <c r="B17" t="n">
-        <v>6.232169395970065</v>
+        <v>3.747950523236492</v>
       </c>
       <c r="C17" t="n">
-        <v>6.232169395970065</v>
+        <v>3.747950523236492</v>
       </c>
       <c r="D17" t="n">
-        <v>5.91590427865732</v>
+        <v>3.474368547140789</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.979189952989901</v>
+        <v>3.570748063206679</v>
       </c>
       <c r="B18" t="n">
-        <v>5.992073360016704</v>
+        <v>3.581780007696779</v>
       </c>
       <c r="C18" t="n">
-        <v>5.992073360016704</v>
+        <v>3.581780007696779</v>
       </c>
       <c r="D18" t="n">
-        <v>5.683860647479233</v>
+        <v>3.317928642280938</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5.749921485531982</v>
+        <v>3.413006651900152</v>
       </c>
       <c r="B19" t="n">
-        <v>5.762485110017292</v>
+        <v>3.423654117178534</v>
       </c>
       <c r="C19" t="n">
-        <v>5.762485110017292</v>
+        <v>3.423654117178534</v>
       </c>
       <c r="D19" t="n">
-        <v>5.462096139280291</v>
+        <v>3.169152944793078</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5.530280746916911</v>
+        <v>3.262650233734414</v>
       </c>
       <c r="B20" t="n">
-        <v>5.542532749871405</v>
+        <v>3.272927316498093</v>
       </c>
       <c r="C20" t="n">
-        <v>5.542532749871405</v>
+        <v>3.272927316498093</v>
       </c>
       <c r="D20" t="n">
-        <v>5.249762639982826</v>
+        <v>3.027427715453745</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5.319632712471119</v>
+        <v>3.119192545636461</v>
       </c>
       <c r="B21" t="n">
-        <v>5.331580662822165</v>
+        <v>3.129112442975185</v>
       </c>
       <c r="C21" t="n">
-        <v>5.331580662822165</v>
+        <v>3.129112442975185</v>
       </c>
       <c r="D21" t="n">
-        <v>5.046239174478113</v>
+        <v>2.892288012176901</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5.117475355140293</v>
+        <v>2.982237994322654</v>
       </c>
       <c r="B22" t="n">
-        <v>5.129126432277232</v>
+        <v>2.991813221804113</v>
       </c>
       <c r="C22" t="n">
-        <v>5.129126432277232</v>
+        <v>2.991813221804113</v>
       </c>
       <c r="D22" t="n">
-        <v>4.85103306262009</v>
+        <v>2.763354490003484</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>4.923384836006437</v>
+        <v>2.851445703835542</v>
       </c>
       <c r="B23" t="n">
-        <v>4.934745939611095</v>
+        <v>2.860688219401832</v>
       </c>
       <c r="C23" t="n">
-        <v>4.934745939611095</v>
+        <v>2.860688219401832</v>
       </c>
       <c r="D23" t="n">
-        <v>4.663727256493686</v>
+        <v>2.640299629863767</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4.736986120787523</v>
+        <v>2.72651015235985</v>
       </c>
       <c r="B24" t="n">
-        <v>4.74806393155075</v>
+        <v>2.735431429999821</v>
       </c>
       <c r="C24" t="n">
-        <v>4.74806393155075</v>
+        <v>2.735431429999821</v>
       </c>
       <c r="D24" t="n">
-        <v>4.483952094496193</v>
+        <v>2.522829539015698</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4.557937051332331</v>
+        <v>2.607150596312204</v>
       </c>
       <c r="B25" t="n">
-        <v>4.56873806556455</v>
+        <v>2.615761672756771</v>
       </c>
       <c r="C25" t="n">
-        <v>4.56873806556455</v>
+        <v>2.615761672756771</v>
       </c>
       <c r="D25" t="n">
-        <v>4.31136997779947</v>
+        <v>2.41067400067954</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4.38591954890209</v>
+        <v>2.49310515821989</v>
       </c>
       <c r="B26" t="n">
-        <v>4.396450099190877</v>
+        <v>2.501416664963074</v>
       </c>
       <c r="C26" t="n">
-        <v>4.396450099190877</v>
+        <v>2.501416664963074</v>
       </c>
       <c r="D26" t="n">
-        <v>4.145666897287907</v>
+        <v>2.303580902575367</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4.220634608194668</v>
+        <v>2.384127398301587</v>
       </c>
       <c r="B27" t="n">
-        <v>4.230900876532014</v>
+        <v>2.392149585478928</v>
       </c>
       <c r="C27" t="n">
-        <v>4.230900876532014</v>
+        <v>2.392149585478928</v>
       </c>
       <c r="D27" t="n">
-        <v>3.986547602481342</v>
+        <v>2.201312998001427</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>4.061799315946009</v>
+        <v>2.279984216537656</v>
       </c>
       <c r="B28" t="n">
-        <v>4.071807342728022</v>
+        <v>2.287726972134223</v>
       </c>
       <c r="C28" t="n">
-        <v>4.071807342728022</v>
+        <v>2.287726972134223</v>
       </c>
       <c r="D28" t="n">
-        <v>3.833732716203779</v>
+        <v>2.103645916907979</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3.909144959702071</v>
+        <v>2.180454474636041</v>
       </c>
       <c r="B29" t="n">
-        <v>3.918900650412562</v>
+        <v>2.187927340885428</v>
       </c>
       <c r="C29" t="n">
-        <v>3.918900650412562</v>
+        <v>2.187927340885428</v>
       </c>
       <c r="D29" t="n">
-        <v>3.686956897519631</v>
+        <v>2.010366853731654</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3.762415731791279</v>
+        <v>2.08532801413169</v>
       </c>
       <c r="B30" t="n">
-        <v>3.771924862330332</v>
+        <v>2.092540202114686</v>
       </c>
       <c r="C30" t="n">
-        <v>3.771924862330332</v>
+        <v>2.092540202114686</v>
       </c>
       <c r="D30" t="n">
-        <v>3.545967577453192</v>
+        <v>1.921273628015214</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3.621367765671797</v>
+        <v>1.994404898471155</v>
       </c>
       <c r="B31" t="n">
-        <v>3.630635986856774</v>
+        <v>2.001365301466151</v>
       </c>
       <c r="C31" t="n">
-        <v>3.630635986856774</v>
+        <v>2.001365301466151</v>
       </c>
       <c r="D31" t="n">
-        <v>3.410524014989084</v>
+        <v>1.836173956153919</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3.485768364598812</v>
+        <v>1.907494787160668</v>
       </c>
       <c r="B32" t="n">
-        <v>3.49480120611814</v>
+        <v>1.914211993059273</v>
       </c>
       <c r="C32" t="n">
-        <v>3.49480120611814</v>
+        <v>1.914211993059273</v>
       </c>
       <c r="D32" t="n">
-        <v>3.280396538753597</v>
+        <v>1.754884847927751</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3.355395347453216</v>
+        <v>1.824416392490249</v>
       </c>
       <c r="B33" t="n">
-        <v>3.364198221435681</v>
+        <v>1.830898695459292</v>
       </c>
       <c r="C33" t="n">
-        <v>3.364198221435681</v>
+        <v>1.830898695459292</v>
       </c>
       <c r="D33" t="n">
-        <v>3.155365902127083</v>
+        <v>1.67723208132711</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3.230036470975923</v>
+        <v>1.744996991860584</v>
       </c>
       <c r="B34" t="n">
-        <v>3.238614675267437</v>
+        <v>1.751252403368985</v>
       </c>
       <c r="C34" t="n">
-        <v>3.238614675267437</v>
+        <v>1.751252403368985</v>
       </c>
       <c r="D34" t="n">
-        <v>3.035222712585432</v>
+        <v>1.603049730307471</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3.109488905892524</v>
+        <v>1.669071980694364</v>
       </c>
       <c r="B35" t="n">
-        <v>3.117847627097632</v>
+        <v>1.675108239976794</v>
       </c>
       <c r="C35" t="n">
-        <v>3.117847627097632</v>
+        <v>1.675108239976794</v>
       </c>
       <c r="D35" t="n">
-        <v>2.919766913588646</v>
+        <v>1.532179731341212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2.99355875412175</v>
+        <v>1.596484457275826</v>
       </c>
       <c r="B36" t="n">
-        <v>3.001703070446922</v>
+        <v>1.602309041289</v>
       </c>
       <c r="C36" t="n">
-        <v>3.001703070446922</v>
+        <v>1.602309041289</v>
       </c>
       <c r="D36" t="n">
-        <v>2.808807306672193</v>
+        <v>1.464471480609665</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2.882060599464273</v>
+        <v>1.527084834289113</v>
       </c>
       <c r="B37" t="n">
-        <v>2.889995483389924</v>
+        <v>1.532704967202984</v>
       </c>
       <c r="C37" t="n">
-        <v>2.889995483389924</v>
+        <v>1.532704967202984</v>
       </c>
       <c r="D37" t="n">
-        <v>2.702161106393694</v>
+        <v>1.399781456893137</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2.77481708698304</v>
+        <v>1.460730473682991</v>
       </c>
       <c r="B38" t="n">
-        <v>2.782547407782412</v>
+        <v>1.466153135940398</v>
       </c>
       <c r="C38" t="n">
-        <v>2.782547407782412</v>
+        <v>1.466153135940398</v>
       </c>
       <c r="D38" t="n">
-        <v>2.599653523493993</v>
+        <v>1.337972866964932</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2.671658527814856</v>
+        <v>1.397285342500856</v>
       </c>
       <c r="B39" t="n">
-        <v>2.679189053938666</v>
+        <v>1.402517279476418</v>
       </c>
       <c r="C39" t="n">
-        <v>2.679189053938666</v>
+        <v>1.402517279476418</v>
       </c>
       <c r="D39" t="n">
-        <v>2.501117373110361</v>
+        <v>1.27891531124942</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2.572422527042666</v>
+        <v>1.336619687914634</v>
       </c>
       <c r="B40" t="n">
-        <v>2.57975792837829</v>
+        <v>1.341667418197545</v>
       </c>
       <c r="C40" t="n">
-        <v>2.57975792837829</v>
+        <v>1.341667418197545</v>
       </c>
       <c r="D40" t="n">
-        <v>2.406392705722112</v>
+        <v>1.22248446805763</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2.476953632740627</v>
+        <v>1.278609730026053</v>
       </c>
       <c r="B41" t="n">
-        <v>2.484098482763102</v>
+        <v>1.28347955334938</v>
       </c>
       <c r="C41" t="n">
-        <v>2.484098482763102</v>
+        <v>1.28347955334938</v>
       </c>
       <c r="D41" t="n">
-        <v>2.315326458994269</v>
+        <v>1.168561795034018</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2.38510300463877</v>
+        <v>1.223137371229631</v>
       </c>
       <c r="B42" t="n">
-        <v>2.392061782458427</v>
+        <v>1.227835376069031</v>
       </c>
       <c r="C42" t="n">
-        <v>2.392061782458427</v>
+        <v>1.227835376069031</v>
       </c>
       <c r="D42" t="n">
-        <v>2.227772128986947</v>
+        <v>1.117034246652613</v>
       </c>
     </row>
   </sheetData>
